--- a/data/b2_candoi/B2 Candói 03-2026.xlsx
+++ b/data/b2_candoi/B2 Candói 03-2026.xlsx
@@ -4891,115 +4891,115 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>482.96</v>
+        <v>486.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>3730.94</v>
+        <v>56972.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46086</v>
+        <v>46089</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>57787.43</v>
+        <v>3998.27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1348.76</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46089</v>
+        <v>46093</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4077.45</v>
+        <v>974.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46091</v>
+        <v>46096</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3200</v>
+        <v>8783.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46093</v>
+        <v>46096</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1070.48</v>
+        <v>994.78</v>
       </c>
     </row>
     <row r="9">
@@ -5008,57 +5008,57 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>9215.440000000001</v>
+        <v>4278.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1010.53</v>
+        <v>1250.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>4113.96</v>
+        <v>1545.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -5067,11 +5067,11 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1461.15</v>
+        <v>1455.68</v>
       </c>
     </row>
     <row r="13">
@@ -5089,79 +5089,79 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>20123.38</v>
+        <v>20428.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46103</v>
+        <v>46101</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>4361.03</v>
+        <v>754.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46106</v>
+        <v>46103</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>10120</v>
+        <v>1988.76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46107</v>
+        <v>46103</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2791.51</v>
+        <v>4450.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>971.1799999999999</v>
+        <v>10120</v>
       </c>
     </row>
     <row r="18">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>4346.13</v>
+        <v>4230.5</v>
       </c>
     </row>
     <row r="19">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>1129.88</v>
+        <v>1063.53</v>
       </c>
     </row>
   </sheetData>
